--- a/order_generation/PO_excel_export/test-3.xlsx
+++ b/order_generation/PO_excel_export/test-3.xlsx
@@ -339,36 +339,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="781050" cy="1266825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -761,7 +731,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>盐城市艳丽工艺品有限公司</t>
+          <t>浙江太平洋纸业</t>
         </is>
       </c>
       <c r="C3" s="16" t="n"/>
@@ -785,7 +755,11 @@
           <t>电话：</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr"/>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>0574-27889688</t>
+        </is>
+      </c>
       <c r="C4" s="16" t="n"/>
       <c r="D4" s="16" t="n"/>
       <c r="E4" s="16" t="n"/>
@@ -796,7 +770,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2025年12月30日</t>
+          <t>2026年02月02日</t>
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
@@ -807,7 +781,11 @@
           <t>联系人：</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr"/>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>小张</t>
+        </is>
+      </c>
       <c r="C5" s="16" t="n"/>
       <c r="D5" s="16" t="n"/>
       <c r="E5" s="16" t="n"/>
@@ -818,7 +796,7 @@
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>郑遥杰</t>
+          <t>孙诚昱</t>
         </is>
       </c>
       <c r="H5" s="16" t="n"/>
@@ -864,26 +842,34 @@
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>EEHB-NBB-2</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="n"/>
+          <t>XLZ</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>[图片未找到] [图片未找到]</t>
+        </is>
+      </c>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>12*25黑色棘皮绒单面，黑色棉绳，烫金logo</t>
+          <t>25*30白底单色logo 28g打字纸</t>
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>1.37</v>
+        <v>0.063</v>
       </c>
       <c r="F7" s="29">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="29" t="inlineStr"/>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>送吉秀</t>
+        </is>
+      </c>
       <c r="H7" s="20" t="n"/>
     </row>
     <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
@@ -944,7 +930,7 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>瑾秀地址：浙江宁波市余姚市陆埠镇五马工业区创利西路 15 号 多多 15258337865</t>
+          <t>宁波市海曙区高桥镇秀丰路58号1栋1楼，小张18668289261</t>
         </is>
       </c>
       <c r="C12" s="25" t="n"/>
@@ -962,7 +948,7 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>款到发货</t>
+          <t>出货后45天凭增值税发票付款</t>
         </is>
       </c>
       <c r="C13" s="25" t="n"/>
@@ -1057,7 +1043,7 @@
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="4">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>备注:打样2套,含税运</t>
+          <t>打样2套</t>
         </is>
       </c>
       <c r="B19" s="25" t="n"/>
@@ -1334,7 +1320,7 @@
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>盐城市艳丽工艺品有限公司</t>
+          <t>浙江太平洋纸业</t>
         </is>
       </c>
       <c r="F69" s="9" t="n"/>
@@ -1383,6 +1369,5 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.78740157480315" bottom="0.590551181102362" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="65" horizontalDpi="360" verticalDpi="360"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>